--- a/data/trilateration_data.xlsx
+++ b/data/trilateration_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emonc\OneDrive\Desktop\RSN Group UWB Project\eece5554-final-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93AB14DC-6468-4B1B-98B9-CA2933435031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F62FD3-9501-4149-9615-251F16AE5E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{ECF9459F-14D8-4B26-8035-2E30A54B085A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="36">
   <si>
     <t>cm</t>
   </si>
@@ -53,9 +53,6 @@
     <t>id2</t>
   </si>
   <si>
-    <t>calibration data</t>
-  </si>
-  <si>
     <t>anchor locations</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>id2 (cm)</t>
   </si>
   <si>
-    <t>robot geometry</t>
-  </si>
-  <si>
     <t>corner</t>
   </si>
   <si>
@@ -135,6 +129,24 @@
   </si>
   <si>
     <t>y (in)</t>
+  </si>
+  <si>
+    <t>Weak Anchor Placement Test</t>
+  </si>
+  <si>
+    <t>Ideal Anchor Placement</t>
+  </si>
+  <si>
+    <t>Anchor Locations</t>
+  </si>
+  <si>
+    <t>Robot Geometry</t>
+  </si>
+  <si>
+    <t>Weak Anchor Placement</t>
+  </si>
+  <si>
+    <t>Calibration Data</t>
   </si>
 </sst>
 </file>
@@ -651,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -676,7 +688,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
@@ -697,14 +708,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1039,124 +1057,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E700C2C4-62D6-4550-AD26-EC19A6843912}">
-  <dimension ref="B1:V30"/>
+  <dimension ref="B1:V42"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="2" max="2" width="13.76953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1328125" customWidth="1"/>
     <col min="4" max="4" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="24" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="6" max="7" width="9.1796875" customWidth="1"/>
     <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.76953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9"/>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.75">
+    <row r="1" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9"/>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B2" s="20"/>
-      <c r="C2" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="21"/>
+      <c r="C2" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="45"/>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
       <c r="G2" s="22"/>
       <c r="H2" s="20"/>
-      <c r="I2" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="46"/>
-      <c r="K2" s="21"/>
+      <c r="I2" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
       <c r="L2" s="22"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="46" t="s">
+      <c r="N2" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="22"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.75">
+      <c r="B3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.75">
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="25"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="24"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="47" t="s">
+      <c r="N3" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="24"/>
+    </row>
+    <row r="4" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B4" s="23"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="23"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="23"/>
+      <c r="Q4" s="24"/>
+    </row>
+    <row r="5" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B5" s="23"/>
+      <c r="C5" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="25"/>
-    </row>
-    <row r="4" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B4" s="23"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="25"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B5" s="23"/>
-      <c r="C5" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="43" t="s">
+      <c r="L5" s="24"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5" s="25"/>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B6" s="23"/>
       <c r="C6" s="18">
         <v>2</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="39">
         <v>48</v>
       </c>
       <c r="E6" s="4">
@@ -1165,31 +1175,31 @@
       <c r="F6" s="5">
         <v>43</v>
       </c>
-      <c r="G6" s="25"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="23"/>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="37">
         <v>1</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="20">
+        <v>20</v>
+      </c>
+      <c r="K6" s="22">
+        <v>-7</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="29">
+      <c r="P6" s="28">
         <v>0</v>
       </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="38">
-        <v>1</v>
-      </c>
-      <c r="O6" s="20">
-        <v>20</v>
-      </c>
-      <c r="P6" s="22">
-        <v>-7</v>
-      </c>
-      <c r="Q6" s="25"/>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B7" s="23"/>
       <c r="C7" s="18">
         <v>4</v>
@@ -1203,31 +1213,31 @@
       <c r="F7" s="7">
         <v>105</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="23"/>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="37">
         <v>2</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="23">
+        <v>20</v>
+      </c>
+      <c r="K7" s="24">
+        <v>7</v>
+      </c>
+      <c r="L7" s="24"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="29">
         <v>0</v>
       </c>
-      <c r="K7" s="31">
+      <c r="P7" s="30">
         <v>4.5</v>
       </c>
-      <c r="L7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="38">
-        <v>2</v>
-      </c>
-      <c r="O7" s="23">
-        <v>20</v>
-      </c>
-      <c r="P7" s="25">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="25"/>
-    </row>
-    <row r="8" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B8" s="23"/>
       <c r="C8" s="18">
         <v>6</v>
@@ -1241,31 +1251,31 @@
       <c r="F8" s="7">
         <v>177</v>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="23"/>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="37">
         <v>3</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="23">
+        <v>0</v>
+      </c>
+      <c r="K8" s="24">
+        <v>7</v>
+      </c>
+      <c r="L8" s="24"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="31">
         <v>4.5</v>
       </c>
-      <c r="K8" s="10">
+      <c r="P8" s="10">
         <v>0</v>
       </c>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="38">
-        <v>3</v>
-      </c>
-      <c r="O8" s="23">
-        <v>0</v>
-      </c>
-      <c r="P8" s="25">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="25"/>
-    </row>
-    <row r="9" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q8" s="24"/>
+    </row>
+    <row r="9" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B9" s="23"/>
       <c r="C9" s="18">
         <v>8</v>
@@ -1279,25 +1289,22 @@
       <c r="F9" s="7">
         <v>225</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
+      <c r="I9" s="38">
+        <v>4</v>
+      </c>
+      <c r="J9" s="25">
+        <v>0</v>
+      </c>
+      <c r="K9" s="27">
+        <v>-7</v>
+      </c>
+      <c r="L9" s="24"/>
       <c r="M9" s="23"/>
-      <c r="N9" s="39">
-        <v>4</v>
-      </c>
-      <c r="O9" s="26">
-        <v>0</v>
-      </c>
-      <c r="P9" s="28">
-        <v>-7</v>
-      </c>
-      <c r="Q9" s="25"/>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q9" s="24"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B10" s="23"/>
       <c r="C10" s="18">
         <v>10</v>
@@ -1311,19 +1318,13 @@
       <c r="F10" s="7">
         <v>306</v>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
+      <c r="L10" s="24"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B11" s="23"/>
       <c r="C11" s="18">
         <v>12</v>
@@ -1337,19 +1338,13 @@
       <c r="F11" s="7">
         <v>393</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
+      <c r="L11" s="24"/>
       <c r="M11" s="23"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="25"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B12" s="23"/>
       <c r="C12" s="18">
         <v>14</v>
@@ -1363,19 +1358,13 @@
       <c r="F12" s="7">
         <v>424</v>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="24"/>
       <c r="M12" s="23"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="25"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q12" s="24"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B13" s="23"/>
       <c r="C13" s="18">
         <v>16</v>
@@ -1389,19 +1378,13 @@
       <c r="F13" s="7">
         <v>491</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="24"/>
       <c r="M13" s="23"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="25"/>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q13" s="24"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B14" s="23"/>
       <c r="C14" s="18">
         <v>18</v>
@@ -1415,24 +1398,18 @@
       <c r="F14" s="7">
         <v>590</v>
       </c>
-      <c r="G14" s="25"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="24"/>
       <c r="M14" s="23"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="25"/>
-    </row>
-    <row r="15" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q14" s="24"/>
+    </row>
+    <row r="15" spans="2:17" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B15" s="23"/>
       <c r="C15" s="19">
         <v>20</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <v>650</v>
       </c>
       <c r="E15" s="9">
@@ -1441,65 +1418,47 @@
       <c r="F15" s="10">
         <v>611</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
+      <c r="L15" s="24"/>
       <c r="M15" s="23"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="25"/>
-    </row>
-    <row r="16" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="Q15" s="24"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.75">
       <c r="B16" s="23"/>
-      <c r="G16" s="25"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="23"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="24"/>
       <c r="M16" s="23"/>
-      <c r="Q16" s="25"/>
-      <c r="R16"/>
-      <c r="S16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
+      <c r="Q16" s="24"/>
     </row>
     <row r="17" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="23"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="24"/>
       <c r="M17" s="23"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="C18" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
       <c r="F18" s="21"/>
       <c r="G18" s="22"/>
       <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
+      <c r="I18" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
@@ -1514,114 +1473,86 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B19" s="23"/>
-      <c r="C19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="G19" s="25"/>
+      <c r="C19" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="23"/>
-      <c r="I19" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="25"/>
+      <c r="I19" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="V19" s="24"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="G20" s="25"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="25"/>
+      <c r="V20" s="24"/>
     </row>
     <row r="21" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B21" s="23"/>
-      <c r="C21" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45" t="s">
+      <c r="C21" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="D21" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="24"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="45" t="s">
+      <c r="I21" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="45" t="s">
+      <c r="N21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="L21" s="45"/>
-      <c r="M21" s="48" t="s">
+      <c r="O21" s="44"/>
+      <c r="P21" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="48" t="s">
+      <c r="Q21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="O21" s="48"/>
-      <c r="P21" s="45" t="s">
+      <c r="R21" s="44"/>
+      <c r="S21" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="45" t="s">
+      <c r="T21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="T21" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="U21" s="45"/>
-      <c r="V21" s="25"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="24"/>
     </row>
     <row r="22" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="F22" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="25"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="24"/>
       <c r="J22" s="14" t="s">
         <v>1</v>
       </c>
@@ -1658,12 +1589,12 @@
       <c r="U22" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="25"/>
+      <c r="V22" s="24"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B23" s="23"/>
       <c r="C23" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="20">
         <v>6</v>
@@ -1674,10 +1605,10 @@
       <c r="F23" s="22">
         <v>0</v>
       </c>
-      <c r="G23" s="25"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="23"/>
       <c r="I23" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="11">
         <v>217</v>
@@ -1715,27 +1646,27 @@
       <c r="U23" s="13">
         <v>183</v>
       </c>
-      <c r="V23" s="25"/>
+      <c r="V23" s="24"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B24" s="23"/>
       <c r="C24" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="23">
         <v>13.5</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24">
         <v>7</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="24">
         <f>180-34.85</f>
         <v>145.15</v>
       </c>
-      <c r="G24" s="25"/>
+      <c r="G24" s="24"/>
       <c r="H24" s="23"/>
       <c r="I24" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" s="6">
         <v>523</v>
@@ -1773,27 +1704,27 @@
       <c r="U24" s="7">
         <v>356</v>
       </c>
-      <c r="V24" s="25"/>
+      <c r="V24" s="24"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B25" s="23"/>
       <c r="C25" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="23">
         <v>18.5</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25">
         <v>6</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="24">
         <f>270+ 16.6</f>
         <v>286.60000000000002</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="23"/>
       <c r="I25" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J25" s="6">
         <v>567</v>
@@ -1831,26 +1762,26 @@
       <c r="U25" s="7">
         <v>461</v>
       </c>
-      <c r="V25" s="25"/>
+      <c r="V25" s="24"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B26" s="23"/>
       <c r="C26" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="23">
         <v>23.5</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26">
         <v>10</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="24">
         <v>270</v>
       </c>
-      <c r="G26" s="25"/>
+      <c r="G26" s="24"/>
       <c r="H26" s="23"/>
       <c r="I26" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" s="6">
         <v>753</v>
@@ -1888,26 +1819,26 @@
       <c r="U26" s="7">
         <v>648</v>
       </c>
-      <c r="V26" s="25"/>
+      <c r="V26" s="24"/>
     </row>
     <row r="27" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="B27" s="23"/>
       <c r="C27" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="26">
+        <v>19</v>
+      </c>
+      <c r="D27" s="25">
         <v>12</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="26">
         <v>1</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="27">
         <v>180</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="24"/>
       <c r="H27" s="23"/>
       <c r="I27" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" s="8">
         <v>423</v>
@@ -1945,80 +1876,428 @@
       <c r="U27" s="10">
         <v>213</v>
       </c>
-      <c r="V27" s="25"/>
+      <c r="V27" s="24"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="G28" s="25"/>
+      <c r="G28" s="24"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="25"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.75">
       <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="G29" s="25"/>
+      <c r="G29" s="24"/>
       <c r="H29" s="23"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="25"/>
+      <c r="V29" s="24"/>
     </row>
     <row r="30" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="28"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="22"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B32" s="23"/>
+      <c r="C32" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="47"/>
+      <c r="M32" s="47"/>
+      <c r="N32" s="47"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="47"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="47"/>
+      <c r="V32" s="24"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B33" s="23"/>
+      <c r="C33" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="47"/>
+      <c r="N33" s="47"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="47"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47"/>
+      <c r="S33" s="47"/>
+      <c r="T33" s="47"/>
+      <c r="U33" s="47"/>
+      <c r="V33" s="24"/>
+    </row>
+    <row r="34" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B34" s="23"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="N34" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q34" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="T34" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="U34" s="49"/>
+      <c r="V34" s="24"/>
+    </row>
+    <row r="35" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B35" s="23"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="47"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="O35" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="R35" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="U35" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="24"/>
+    </row>
+    <row r="36" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B36" s="23"/>
+      <c r="C36" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="28">
+        <v>0</v>
+      </c>
+      <c r="F36" s="47"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="50">
+        <v>209</v>
+      </c>
+      <c r="K36" s="51">
+        <v>189</v>
+      </c>
+      <c r="L36" s="52">
+        <v>211</v>
+      </c>
+      <c r="M36" s="50">
+        <v>166</v>
+      </c>
+      <c r="N36" s="51">
+        <v>134</v>
+      </c>
+      <c r="O36" s="52">
+        <v>153</v>
+      </c>
+      <c r="P36" s="50">
+        <v>204</v>
+      </c>
+      <c r="Q36" s="51">
+        <v>173</v>
+      </c>
+      <c r="R36" s="52">
+        <v>194</v>
+      </c>
+      <c r="S36" s="50">
+        <v>236</v>
+      </c>
+      <c r="T36" s="51">
+        <v>181</v>
+      </c>
+      <c r="U36" s="52">
+        <v>187</v>
+      </c>
+      <c r="V36" s="24"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B37" s="23"/>
+      <c r="C37" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="29">
+        <v>0</v>
+      </c>
+      <c r="E37" s="30">
+        <v>1</v>
+      </c>
+      <c r="F37" s="47"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="47"/>
+      <c r="M37" s="47"/>
+      <c r="N37" s="47"/>
+      <c r="O37" s="47"/>
+      <c r="P37" s="47"/>
+      <c r="Q37" s="47"/>
+      <c r="R37" s="47"/>
+      <c r="S37" s="47"/>
+      <c r="T37" s="47"/>
+      <c r="U37" s="47"/>
+      <c r="V37" s="24"/>
+    </row>
+    <row r="38" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B38" s="23"/>
+      <c r="C38" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="31">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0</v>
+      </c>
+      <c r="F38" s="47"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="47"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="47"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47"/>
+      <c r="S38" s="47"/>
+      <c r="T38" s="47"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="24"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B39" s="23"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="47"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="47"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47"/>
+      <c r="S39" s="47"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="24"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B40" s="23"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="47"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="47"/>
+      <c r="N40" s="47"/>
+      <c r="O40" s="47"/>
+      <c r="P40" s="47"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47"/>
+      <c r="S40" s="47"/>
+      <c r="T40" s="47"/>
+      <c r="U40" s="47"/>
+      <c r="V40" s="24"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="B41" s="23"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="47"/>
+      <c r="N41" s="47"/>
+      <c r="O41" s="47"/>
+      <c r="P41" s="47"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47"/>
+      <c r="S41" s="47"/>
+      <c r="T41" s="47"/>
+      <c r="U41" s="47"/>
+      <c r="V41" s="24"/>
+    </row>
+    <row r="42" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:O3"/>
+  <mergeCells count="11">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/trilateration_data.xlsx
+++ b/data/trilateration_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emonc\OneDrive\Desktop\RSN Group UWB Project\eece5554-final-project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Geisel\Documents\GitHub\eece5554-final-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93AB14DC-6468-4B1B-98B9-CA2933435031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0AF3E7-E2AE-41CB-BE32-AEA175325849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{ECF9459F-14D8-4B26-8035-2E30A54B085A}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{ECF9459F-14D8-4B26-8035-2E30A54B085A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>cm</t>
   </si>
@@ -136,11 +136,20 @@
   <si>
     <t>y (in)</t>
   </si>
+  <si>
+    <t>Corrected Reading id0(ft)</t>
+  </si>
+  <si>
+    <t>Corrected Reading id1(ft)</t>
+  </si>
+  <si>
+    <t>Corrected Reading id2(ft)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -651,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -676,7 +685,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
@@ -697,20 +705,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{CE577357-5C3A-4695-AE03-D07DACAD0106}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -720,6 +729,1426 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>id0 (cm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.50295600927482698"/>
+                  <c:y val="0.59879630899553293"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$6:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$6:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>356</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>483</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>650</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-25D3-438A-9FD8-9AFFE5F68FEB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>id1 (cm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.29997047938361415"/>
+                  <c:y val="0.59941894847370747"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$6:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$6:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>352</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>427</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>463</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>564</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>630</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-25D3-438A-9FD8-9AFFE5F68FEB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>id2 (cm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.7665190764225788E-2"/>
+                  <c:y val="0.54655918688180316"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$6:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$6:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>393</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>424</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>491</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>611</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-25D3-438A-9FD8-9AFFE5F68FEB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="518535568"/>
+        <c:axId val="518536048"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="518535568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="518536048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="518536048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="518535568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>566551</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38594</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>148441</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4640F001-4362-4118-F890-CD947383794C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1039,22 +2468,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E700C2C4-62D6-4550-AD26-EC19A6843912}">
-  <dimension ref="B1:V30"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="B1:V42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="13.76953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="24" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" customWidth="1"/>
-    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.76953125" customWidth="1"/>
+    <col min="2" max="2" width="13.7890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.05078125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.15625" customWidth="1"/>
+    <col min="12" max="12" width="11.47265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9"/>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.75">
+    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="20"/>
       <c r="C2" s="21" t="s">
         <v>4</v>
@@ -1064,99 +2491,86 @@
       <c r="F2" s="21"/>
       <c r="G2" s="22"/>
       <c r="H2" s="20"/>
-      <c r="I2" s="46" t="s">
+      <c r="I2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="45"/>
       <c r="K2" s="21"/>
       <c r="L2" s="22"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="46" t="s">
+      <c r="N2" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="46"/>
+      <c r="O2" s="45"/>
       <c r="P2" s="21"/>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.75">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="G3" s="25"/>
+      <c r="G3" s="24"/>
       <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="25"/>
+      <c r="L3" s="24"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="47" t="s">
+      <c r="N3" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="25"/>
-    </row>
-    <row r="4" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="O3" s="46"/>
+      <c r="Q3" s="24"/>
+    </row>
+    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B4" s="23"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="25"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="23"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="24"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="25"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q4" s="24"/>
+    </row>
+    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B5" s="23"/>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="23"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="43" t="s">
+      <c r="I5" s="44"/>
+      <c r="J5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="25"/>
+      <c r="L5" s="24"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="42" t="s">
+      <c r="N5" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="P5" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="25"/>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="23"/>
       <c r="C6" s="18">
         <v>2</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="39">
         <v>48</v>
       </c>
       <c r="E6" s="4">
@@ -1165,20 +2579,20 @@
       <c r="F6" s="5">
         <v>43</v>
       </c>
-      <c r="G6" s="25"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="23"/>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="32" t="s">
         <v>1</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="28">
         <v>0</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="24"/>
       <c r="M6" s="23"/>
-      <c r="N6" s="38">
+      <c r="N6" s="37">
         <v>1</v>
       </c>
       <c r="O6" s="20">
@@ -1187,9 +2601,9 @@
       <c r="P6" s="22">
         <v>-7</v>
       </c>
-      <c r="Q6" s="25"/>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="23"/>
       <c r="C7" s="18">
         <v>4</v>
@@ -1203,31 +2617,31 @@
       <c r="F7" s="7">
         <v>105</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="23"/>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>0</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="30">
         <v>4.5</v>
       </c>
-      <c r="L7" s="25"/>
+      <c r="L7" s="24"/>
       <c r="M7" s="23"/>
-      <c r="N7" s="38">
+      <c r="N7" s="37">
         <v>2</v>
       </c>
       <c r="O7" s="23">
         <v>20</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="24">
         <v>7</v>
       </c>
-      <c r="Q7" s="25"/>
-    </row>
-    <row r="8" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B8" s="23"/>
       <c r="C8" s="18">
         <v>6</v>
@@ -1241,31 +2655,31 @@
       <c r="F8" s="7">
         <v>177</v>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="23"/>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="31">
         <v>4.5</v>
       </c>
       <c r="K8" s="10">
         <v>0</v>
       </c>
-      <c r="L8" s="25"/>
+      <c r="L8" s="24"/>
       <c r="M8" s="23"/>
-      <c r="N8" s="38">
+      <c r="N8" s="37">
         <v>3</v>
       </c>
       <c r="O8" s="23">
         <v>0</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="24">
         <v>7</v>
       </c>
-      <c r="Q8" s="25"/>
-    </row>
-    <row r="9" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q8" s="24"/>
+    </row>
+    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B9" s="23"/>
       <c r="C9" s="18">
         <v>8</v>
@@ -1279,25 +2693,22 @@
       <c r="F9" s="7">
         <v>225</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="24"/>
       <c r="M9" s="23"/>
-      <c r="N9" s="39">
+      <c r="N9" s="38">
         <v>4</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="25">
         <v>0</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="27">
         <v>-7</v>
       </c>
-      <c r="Q9" s="25"/>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q9" s="24"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="23"/>
       <c r="C10" s="18">
         <v>10</v>
@@ -1311,19 +2722,13 @@
       <c r="F10" s="7">
         <v>306</v>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
+      <c r="L10" s="24"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q10" s="24"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="23"/>
       <c r="C11" s="18">
         <v>12</v>
@@ -1337,19 +2742,13 @@
       <c r="F11" s="7">
         <v>393</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
+      <c r="L11" s="24"/>
       <c r="M11" s="23"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="25"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q11" s="24"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="23"/>
       <c r="C12" s="18">
         <v>14</v>
@@ -1363,19 +2762,13 @@
       <c r="F12" s="7">
         <v>424</v>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="24"/>
       <c r="M12" s="23"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="25"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q12" s="24"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="23"/>
       <c r="C13" s="18">
         <v>16</v>
@@ -1389,19 +2782,13 @@
       <c r="F13" s="7">
         <v>491</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="24"/>
       <c r="M13" s="23"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="25"/>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q13" s="24"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="23"/>
       <c r="C14" s="18">
         <v>18</v>
@@ -1415,24 +2802,18 @@
       <c r="F14" s="7">
         <v>590</v>
       </c>
-      <c r="G14" s="25"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="24"/>
       <c r="M14" s="23"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="25"/>
-    </row>
-    <row r="15" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Q14" s="24"/>
+    </row>
+    <row r="15" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B15" s="23"/>
       <c r="C15" s="19">
         <v>20</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <v>650</v>
       </c>
       <c r="E15" s="9">
@@ -1441,55 +2822,33 @@
       <c r="F15" s="10">
         <v>611</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
+      <c r="L15" s="24"/>
       <c r="M15" s="23"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="25"/>
-    </row>
-    <row r="16" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="Q15" s="24"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="23"/>
-      <c r="G16" s="25"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="23"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="24"/>
       <c r="M16" s="23"/>
-      <c r="Q16" s="25"/>
-      <c r="R16"/>
-      <c r="S16"/>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-    </row>
-    <row r="17" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
+      <c r="Q16" s="24"/>
+    </row>
+    <row r="17" spans="2:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="23"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="24"/>
       <c r="M17" s="23"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="Q17" s="24"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
@@ -1512,116 +2871,84 @@
       <c r="U18" s="21"/>
       <c r="V18" s="22"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.75">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="23"/>
-      <c r="C19" s="24" t="s">
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="G19" s="25"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="23"/>
-      <c r="I19" s="24" t="s">
+      <c r="I19" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="25"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V19" s="24"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="G20" s="25"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="25"/>
-    </row>
-    <row r="21" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="V20" s="24"/>
+    </row>
+    <row r="21" spans="2:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B21" s="23"/>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45" t="s">
+      <c r="E21" s="44"/>
+      <c r="F21" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="45" t="s">
+      <c r="I21" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="45" t="s">
+      <c r="J21" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="45" t="s">
+      <c r="K21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="L21" s="45"/>
-      <c r="M21" s="48" t="s">
+      <c r="L21" s="44"/>
+      <c r="M21" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="48" t="s">
+      <c r="N21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="O21" s="48"/>
-      <c r="P21" s="45" t="s">
+      <c r="O21" s="44"/>
+      <c r="P21" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="45" t="s">
+      <c r="Q21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45" t="s">
+      <c r="R21" s="44"/>
+      <c r="S21" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="T21" s="45" t="s">
+      <c r="T21" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="U21" s="45"/>
-      <c r="V21" s="25"/>
-    </row>
-    <row r="22" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="U21" s="44"/>
+      <c r="V21" s="24"/>
+    </row>
+    <row r="22" spans="2:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="25"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="24"/>
       <c r="J22" s="14" t="s">
         <v>1</v>
       </c>
@@ -1658,9 +2985,9 @@
       <c r="U22" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="25"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V22" s="24"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="23"/>
       <c r="C23" s="17" t="s">
         <v>16</v>
@@ -1674,7 +3001,7 @@
       <c r="F23" s="22">
         <v>0</v>
       </c>
-      <c r="G23" s="25"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="23"/>
       <c r="I23" s="17" t="s">
         <v>16</v>
@@ -1715,9 +3042,9 @@
       <c r="U23" s="13">
         <v>183</v>
       </c>
-      <c r="V23" s="25"/>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V23" s="24"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="23"/>
       <c r="C24" s="18" t="s">
         <v>17</v>
@@ -1725,14 +3052,14 @@
       <c r="D24" s="23">
         <v>13.5</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24">
         <v>7</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="24">
         <f>180-34.85</f>
         <v>145.15</v>
       </c>
-      <c r="G24" s="25"/>
+      <c r="G24" s="24"/>
       <c r="H24" s="23"/>
       <c r="I24" s="18" t="s">
         <v>17</v>
@@ -1773,9 +3100,9 @@
       <c r="U24" s="7">
         <v>356</v>
       </c>
-      <c r="V24" s="25"/>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V24" s="24"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="23"/>
       <c r="C25" s="18" t="s">
         <v>18</v>
@@ -1783,14 +3110,14 @@
       <c r="D25" s="23">
         <v>18.5</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25">
         <v>6</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="24">
         <f>270+ 16.6</f>
         <v>286.60000000000002</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="23"/>
       <c r="I25" s="18" t="s">
         <v>18</v>
@@ -1831,9 +3158,9 @@
       <c r="U25" s="7">
         <v>461</v>
       </c>
-      <c r="V25" s="25"/>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V25" s="24"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="23"/>
       <c r="C26" s="18" t="s">
         <v>19</v>
@@ -1841,13 +3168,13 @@
       <c r="D26" s="23">
         <v>23.5</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26">
         <v>10</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="24">
         <v>270</v>
       </c>
-      <c r="G26" s="25"/>
+      <c r="G26" s="24"/>
       <c r="H26" s="23"/>
       <c r="I26" s="18" t="s">
         <v>19</v>
@@ -1888,23 +3215,23 @@
       <c r="U26" s="7">
         <v>648</v>
       </c>
-      <c r="V26" s="25"/>
-    </row>
-    <row r="27" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="V26" s="24"/>
+    </row>
+    <row r="27" spans="2:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B27" s="23"/>
       <c r="C27" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="25">
         <v>12</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="26">
         <v>1</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="27">
         <v>180</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="24"/>
       <c r="H27" s="23"/>
       <c r="I27" s="19" t="s">
         <v>20</v>
@@ -1945,74 +3272,193 @@
       <c r="U27" s="10">
         <v>213</v>
       </c>
-      <c r="V27" s="25"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V27" s="24"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="G28" s="25"/>
+      <c r="G28" s="24"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="25"/>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.75">
+      <c r="V28" s="24"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="G29" s="25"/>
+      <c r="G29" s="24"/>
       <c r="H29" s="23"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="25"/>
-    </row>
-    <row r="30" spans="2:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="28"/>
+      <c r="V29" s="24"/>
+    </row>
+    <row r="30" spans="2:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C33">
+        <f>(D6+27.876)/32.542</f>
+        <v>2.3316329666277427</v>
+      </c>
+      <c r="D33">
+        <f>(E6+22.333)/31.885</f>
+        <v>2.2058334640112904</v>
+      </c>
+      <c r="E33">
+        <f>(F6+22.2)/32.609</f>
+        <v>1.9994480051519519</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C34">
+        <f t="shared" ref="C34:C46" si="0">(D7+27.876)/32.542</f>
+        <v>4.2675926494991092</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ref="D34:D42" si="1">(E7+22.333)/31.885</f>
+        <v>4.1503214677748153</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ref="E34:E42" si="2">(F7+22.2)/32.609</f>
+        <v>3.9007635928731332</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>5.9269866633888508</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>6.1575348910145831</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>6.1087429850654722</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>7.8629463462602169</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>7.8511212168731372</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>7.5807292465270315</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>9.7067174728043746</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>9.7328838011604191</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>10.064706062743413</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>11.796324749554421</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>11.740097224400186</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>12.732681161642491</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>13.763013951201522</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>14.09230045475929</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>13.68333895550308</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>15.698973634072889</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="1"/>
+        <v>15.221358005331659</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="2"/>
+        <v>15.737986445459843</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>17.819310429598669</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="1"/>
+        <v>18.388991688881916</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="2"/>
+        <v>18.773958109724308</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>20.830803269620795</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="1"/>
+        <v>20.458930531597929</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>19.417952099113741</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2022,5 +3468,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>